--- a/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
+++ b/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -116,6 +116,9 @@
   </si>
   <si>
     <t xml:space="preserve">Černošice - Praha-Západ: Na okraji pole u obce Černošice - Nová Vráž. 15 km JZ Prahy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST_5</t>
   </si>
 </sst>
 </file>
@@ -322,7 +325,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultColWidth="19.61328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="1" style="1" width="19.61"/>
@@ -483,6 +486,41 @@
         <v>2017</v>
       </c>
       <c r="N4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
+++ b/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -64,15 +64,15 @@
     <t xml:space="preserve">scientificName</t>
   </si>
   <si>
+    <t xml:space="preserve">MP B0073/0069201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreservedSpecimen</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST_1</t>
   </si>
   <si>
-    <t xml:space="preserve">PreservedSpecimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MP B0073/0069201</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hadinec J.</t>
   </si>
   <si>
@@ -88,27 +88,36 @@
     <t xml:space="preserve">Šumberová Kateřina, Mgr., Ph.D.</t>
   </si>
   <si>
+    <t xml:space="preserve">MP B0073/0071590</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST_10</t>
   </si>
   <si>
-    <t xml:space="preserve">MP B0073/0071590</t>
-  </si>
-  <si>
     <t xml:space="preserve">Faltys Vladimír, RNDr.</t>
   </si>
   <si>
+    <t xml:space="preserve">note on occurrence</t>
+  </si>
+  <si>
     <t xml:space="preserve">29.5.1973</t>
   </si>
   <si>
     <t xml:space="preserve">Meziříčí u Kadaně - Severozápadní Čechy. Kadaň (Z): okolí obce Meziříčí.</t>
   </si>
   <si>
+    <t xml:space="preserve">Hepatica nobilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abies alba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP B0073/0096052</t>
+  </si>
+  <si>
     <t xml:space="preserve">TEST_11</t>
   </si>
   <si>
-    <t xml:space="preserve">MP B0073/0096052</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hanousek Jindřich</t>
   </si>
   <si>
@@ -116,6 +125,9 @@
   </si>
   <si>
     <t xml:space="preserve">Černošice - Praha-Západ: Na okraji pole u obce Černošice - Nová Vráž. 15 km JZ Prahy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MP B0073/0096053</t>
   </si>
   <si>
     <t xml:space="preserve">TEST_5</t>
@@ -429,11 +441,14 @@
       <c r="D3" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>50.123456</v>
@@ -442,7 +457,7 @@
         <v>18.7654321</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>21</v>
@@ -451,27 +466,27 @@
         <v>2017</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>300</v>
@@ -491,22 +506,22 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>300</v>

--- a/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
+++ b/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -70,7 +70,7 @@
     <t xml:space="preserve">PreservedSpecimen</t>
   </si>
   <si>
-    <t xml:space="preserve">TEST_1</t>
+    <t xml:space="preserve">TEST 1</t>
   </si>
   <si>
     <t xml:space="preserve">Hadinec J.</t>
@@ -91,7 +91,7 @@
     <t xml:space="preserve">MP B0073/0071590</t>
   </si>
   <si>
-    <t xml:space="preserve">TEST_10</t>
+    <t xml:space="preserve">TEST 10</t>
   </si>
   <si>
     <t xml:space="preserve">Faltys Vladimír, RNDr.</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">MP B0073/0096052</t>
   </si>
   <si>
-    <t xml:space="preserve">TEST_11</t>
+    <t xml:space="preserve">TEST 11</t>
   </si>
   <si>
     <t xml:space="preserve">Hanousek Jindřich</t>
@@ -130,7 +130,7 @@
     <t xml:space="preserve">MP B0073/0096053</t>
   </si>
   <si>
-    <t xml:space="preserve">TEST_5</t>
+    <t xml:space="preserve">TEST 5</t>
   </si>
 </sst>
 </file>
@@ -338,7 +338,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N5"/>
-  <sheetFormatPr defaultColWidth="19.61328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="19.61328125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="1" style="1" width="19.61"/>
   </cols>

--- a/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
+++ b/htdocs/tests/Cases/Integration/files/cetaf_sid.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -64,6 +64,9 @@
     <t xml:space="preserve">scientificName</t>
   </si>
   <si>
+    <t xml:space="preserve">verbatimEventDate</t>
+  </si>
+  <si>
     <t xml:space="preserve">MP B0073/0069201</t>
   </si>
   <si>
@@ -76,7 +79,7 @@
     <t xml:space="preserve">Hadinec J.</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5.1980</t>
+    <t xml:space="preserve">2022-07-04</t>
   </si>
   <si>
     <t xml:space="preserve">Slovensko - Jižní Slovensko; Cerová vrchovina. Šiatorská Bukovinka: na písčitém okraji pole při červ. znač. turistické cestě Z obce, ca 300 m n. m.</t>
@@ -88,6 +91,9 @@
     <t xml:space="preserve">Šumberová Kateřina, Mgr., Ph.D.</t>
   </si>
   <si>
+    <t xml:space="preserve">2022.07.04</t>
+  </si>
+  <si>
     <t xml:space="preserve">MP B0073/0071590</t>
   </si>
   <si>
@@ -100,7 +106,7 @@
     <t xml:space="preserve">note on occurrence</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5.1973</t>
+    <t xml:space="preserve">2021-08-25</t>
   </si>
   <si>
     <t xml:space="preserve">Meziříčí u Kadaně - Severozápadní Čechy. Kadaň (Z): okolí obce Meziříčí.</t>
@@ -121,7 +127,7 @@
     <t xml:space="preserve">Hanousek Jindřich</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4.1988</t>
+    <t xml:space="preserve">1933-08</t>
   </si>
   <si>
     <t xml:space="preserve">Černošice - Praha-Západ: Na okraji pole u obce Černošice - Nová Vráž. 15 km JZ Prahy.</t>
@@ -234,37 +240,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -337,7 +343,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultColWidth="19.61328125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="1" style="1" width="19.61"/>
@@ -386,25 +392,28 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="0" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="F2" s="0" t="s">
+        <v>19</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>300</v>
@@ -416,39 +425,42 @@
         <v>30.123</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="O2" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>28</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>50.123456</v>
@@ -457,86 +469,95 @@
         <v>18.7654321</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="O3" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>35</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" s="1" t="n">
         <v>300</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M4" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <v>8.1933</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>300</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" s="1" t="n">
         <v>2017</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="O5" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
